--- a/LoanOfficer-A/2023/83 sunanda.xlsx
+++ b/LoanOfficer-A/2023/83 sunanda.xlsx
@@ -609,7 +609,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -816,7 +816,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -825,7 +825,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>1800</v>
+        <v>5400</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -860,7 +860,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>158400</v>
+        <v>154800</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -964,9 +964,15 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="1"/>
+      <c r="B6" s="3">
+        <v>45622</v>
+      </c>
+      <c r="C6" s="4">
+        <v>600</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
       <c r="E6" s="1">
         <v>34</v>
       </c>
@@ -990,9 +996,15 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="1"/>
+      <c r="B7" s="3">
+        <v>45623</v>
+      </c>
+      <c r="C7" s="4">
+        <v>600</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
       <c r="E7" s="1">
         <v>35</v>
       </c>
@@ -1016,9 +1028,15 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="1"/>
+      <c r="B8" s="3">
+        <v>45624</v>
+      </c>
+      <c r="C8" s="4">
+        <v>600</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
       <c r="E8" s="1">
         <v>36</v>
       </c>
@@ -1042,9 +1060,15 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
+      <c r="B9" s="3">
+        <v>45625</v>
+      </c>
+      <c r="C9" s="4">
+        <v>600</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
       <c r="E9" s="1">
         <v>37</v>
       </c>
@@ -1068,9 +1092,15 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
+      <c r="B10" s="3">
+        <v>45627</v>
+      </c>
+      <c r="C10" s="4">
+        <v>600</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
       <c r="E10" s="1">
         <v>38</v>
       </c>
@@ -1094,9 +1124,15 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="3">
+        <v>45627</v>
+      </c>
+      <c r="C11" s="4">
+        <v>600</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
       <c r="E11" s="1">
         <v>39</v>
       </c>

--- a/LoanOfficer-A/2023/83 sunanda.xlsx
+++ b/LoanOfficer-A/2023/83 sunanda.xlsx
@@ -609,7 +609,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -816,7 +816,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -825,7 +825,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>5400</v>
+        <v>7800</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -860,7 +860,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>154800</v>
+        <v>152400</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1156,9 +1156,15 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="3">
+        <v>45629</v>
+      </c>
+      <c r="C12" s="4">
+        <v>600</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
       <c r="E12" s="1">
         <v>40</v>
       </c>
@@ -1182,9 +1188,15 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="3">
+        <v>45629</v>
+      </c>
+      <c r="C13" s="4">
+        <v>600</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
       <c r="E13" s="1">
         <v>41</v>
       </c>
@@ -1208,9 +1220,15 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="1"/>
+      <c r="B14" s="3">
+        <v>45630</v>
+      </c>
+      <c r="C14" s="4">
+        <v>600</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
       <c r="E14" s="1">
         <v>42</v>
       </c>
@@ -1234,9 +1252,15 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
+      <c r="B15" s="3">
+        <v>45631</v>
+      </c>
+      <c r="C15" s="4">
+        <v>600</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
       <c r="E15" s="1">
         <v>43</v>
       </c>

--- a/LoanOfficer-A/2023/83 sunanda.xlsx
+++ b/LoanOfficer-A/2023/83 sunanda.xlsx
@@ -104,7 +104,7 @@
     <t>Paid (weeks):</t>
   </si>
   <si>
-    <t>sunanda</t>
+    <t>Date of completion</t>
   </si>
 </sst>
 </file>
@@ -220,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -281,6 +281,9 @@
     </xf>
     <xf numFmtId="15" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -627,8 +630,8 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="13"/>
@@ -708,20 +711,20 @@
       <c r="C16" s="14"/>
     </row>
     <row r="17" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="22"/>
+      <c r="C17" s="23"/>
     </row>
     <row r="19" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
     </row>
     <row r="21" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="22"/>
+      <c r="C21" s="23"/>
     </row>
     <row r="22" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B22" s="14"/>
@@ -816,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -825,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>7800</v>
+        <v>11400</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -843,7 +846,10 @@
       <c r="F2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="7"/>
+      <c r="G2" s="21">
+        <f>B3+G1-1</f>
+        <v>45885</v>
+      </c>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
       <c r="J2" s="7" t="s">
@@ -851,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -860,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>152400</v>
+        <v>148800</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1284,9 +1290,15 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
+      <c r="B16" s="3">
+        <v>45633</v>
+      </c>
+      <c r="C16" s="4">
+        <v>600</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
       <c r="E16" s="1">
         <v>44</v>
       </c>
@@ -1310,9 +1322,15 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="3">
+        <v>45634</v>
+      </c>
+      <c r="C17" s="4">
+        <v>600</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
       <c r="E17" s="1">
         <v>45</v>
       </c>
@@ -1336,9 +1354,15 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="1"/>
+      <c r="B18" s="3">
+        <v>45637</v>
+      </c>
+      <c r="C18" s="4">
+        <v>600</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
       <c r="E18" s="1">
         <v>46</v>
       </c>
@@ -1362,9 +1386,15 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="1"/>
+      <c r="B19" s="3">
+        <v>45641</v>
+      </c>
+      <c r="C19" s="4">
+        <v>600</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
       <c r="E19" s="1">
         <v>47</v>
       </c>
@@ -1388,9 +1418,15 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="1"/>
+      <c r="B20" s="3">
+        <v>45642</v>
+      </c>
+      <c r="C20" s="4">
+        <v>600</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
       <c r="E20" s="1">
         <v>48</v>
       </c>
@@ -1414,9 +1450,15 @@
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="1"/>
+      <c r="B21" s="3">
+        <v>45646</v>
+      </c>
+      <c r="C21" s="4">
+        <v>600</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
       <c r="E21" s="1">
         <v>49</v>
       </c>

--- a/LoanOfficer-A/2023/83 sunanda.xlsx
+++ b/LoanOfficer-A/2023/83 sunanda.xlsx
@@ -612,7 +612,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>11400</v>
+        <v>13200</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>148800</v>
+        <v>147000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1451,7 +1451,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="3">
-        <v>45646</v>
+        <v>45645</v>
       </c>
       <c r="C21" s="4">
         <v>600</v>
@@ -1482,9 +1482,15 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="1"/>
+      <c r="B22" s="3">
+        <v>45646</v>
+      </c>
+      <c r="C22" s="4">
+        <v>600</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
@@ -1508,9 +1514,15 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="1"/>
+      <c r="B23" s="3">
+        <v>45650</v>
+      </c>
+      <c r="C23" s="4">
+        <v>600</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
       <c r="E23" s="1">
         <v>51</v>
       </c>
@@ -1534,9 +1546,15 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="1"/>
+      <c r="B24" s="3">
+        <v>45653</v>
+      </c>
+      <c r="C24" s="4">
+        <v>600</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
       <c r="E24" s="1">
         <v>52</v>
       </c>

--- a/LoanOfficer-A/2023/83 sunanda.xlsx
+++ b/LoanOfficer-A/2023/83 sunanda.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>13200</v>
+        <v>20400</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>147000</v>
+        <v>139800</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -886,9 +886,15 @@
       <c r="E3" s="1">
         <v>31</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="1"/>
+      <c r="F3" s="3">
+        <v>45663</v>
+      </c>
+      <c r="G3" s="4">
+        <v>600</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
       <c r="I3" s="1">
         <v>61</v>
       </c>
@@ -918,9 +924,15 @@
       <c r="E4" s="1">
         <v>32</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="1"/>
+      <c r="F4" s="3">
+        <v>45664</v>
+      </c>
+      <c r="G4" s="4">
+        <v>600</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
       <c r="I4" s="1">
         <v>62</v>
       </c>
@@ -950,9 +962,15 @@
       <c r="E5" s="1">
         <v>33</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="1"/>
+      <c r="F5" s="3">
+        <v>45665</v>
+      </c>
+      <c r="G5" s="4">
+        <v>600</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
       <c r="I5" s="1">
         <v>63</v>
       </c>
@@ -982,9 +1000,15 @@
       <c r="E6" s="1">
         <v>34</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="1"/>
+      <c r="F6" s="3">
+        <v>45667</v>
+      </c>
+      <c r="G6" s="4">
+        <v>600</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
       <c r="I6" s="1">
         <v>64</v>
       </c>
@@ -1578,9 +1602,15 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="1"/>
+      <c r="B25" s="3">
+        <v>45655</v>
+      </c>
+      <c r="C25" s="4">
+        <v>600</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
       <c r="E25" s="1">
         <v>53</v>
       </c>
@@ -1604,9 +1634,15 @@
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="1"/>
+      <c r="B26" s="3">
+        <v>45656</v>
+      </c>
+      <c r="C26" s="4">
+        <v>600</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
       <c r="E26" s="1">
         <v>54</v>
       </c>
@@ -1630,9 +1666,15 @@
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="1"/>
+      <c r="B27" s="3">
+        <v>45657</v>
+      </c>
+      <c r="C27" s="4">
+        <v>600</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
       <c r="E27" s="1">
         <v>55</v>
       </c>
@@ -1656,9 +1698,15 @@
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="1"/>
+      <c r="B28" s="3">
+        <v>45658</v>
+      </c>
+      <c r="C28" s="4">
+        <v>600</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
       <c r="E28" s="1">
         <v>56</v>
       </c>
@@ -1682,9 +1730,15 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="1"/>
+      <c r="B29" s="3">
+        <v>45659</v>
+      </c>
+      <c r="C29" s="4">
+        <v>600</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
       <c r="E29" s="1">
         <v>57</v>
       </c>
@@ -1708,9 +1762,15 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="1"/>
+      <c r="B30" s="3">
+        <v>45661</v>
+      </c>
+      <c r="C30" s="4">
+        <v>600</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
       <c r="E30" s="1">
         <v>58</v>
       </c>
@@ -1734,9 +1794,15 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="1"/>
+      <c r="B31" s="3">
+        <v>45661</v>
+      </c>
+      <c r="C31" s="4">
+        <v>600</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
       <c r="E31" s="1">
         <v>59</v>
       </c>
@@ -1760,9 +1826,15 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="1"/>
+      <c r="B32" s="3">
+        <v>45661</v>
+      </c>
+      <c r="C32" s="4">
+        <v>600</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
       <c r="E32" s="1">
         <v>60</v>
       </c>

--- a/LoanOfficer-A/2023/83 sunanda.xlsx
+++ b/LoanOfficer-A/2023/83 sunanda.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>20400</v>
+        <v>23400</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>139800</v>
+        <v>136800</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1038,9 +1038,15 @@
       <c r="E7" s="1">
         <v>35</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="1"/>
+      <c r="F7" s="3">
+        <v>45669</v>
+      </c>
+      <c r="G7" s="4">
+        <v>600</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
       <c r="I7" s="1">
         <v>65</v>
       </c>
@@ -1070,9 +1076,15 @@
       <c r="E8" s="1">
         <v>36</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="1"/>
+      <c r="F8" s="3">
+        <v>45671</v>
+      </c>
+      <c r="G8" s="4">
+        <v>600</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
       <c r="I8" s="1">
         <v>66</v>
       </c>
@@ -1102,9 +1114,15 @@
       <c r="E9" s="1">
         <v>37</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="1"/>
+      <c r="F9" s="3">
+        <v>45673</v>
+      </c>
+      <c r="G9" s="4">
+        <v>600</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
       <c r="I9" s="1">
         <v>67</v>
       </c>
@@ -1134,9 +1152,15 @@
       <c r="E10" s="1">
         <v>38</v>
       </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="1"/>
+      <c r="F10" s="3">
+        <v>45674</v>
+      </c>
+      <c r="G10" s="4">
+        <v>600</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
       <c r="I10" s="1">
         <v>68</v>
       </c>
@@ -1166,9 +1190,15 @@
       <c r="E11" s="1">
         <v>39</v>
       </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="1"/>
+      <c r="F11" s="3">
+        <v>45675</v>
+      </c>
+      <c r="G11" s="4">
+        <v>600</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
       <c r="I11" s="1">
         <v>69</v>
       </c>

--- a/LoanOfficer-A/2023/83 sunanda.xlsx
+++ b/LoanOfficer-A/2023/83 sunanda.xlsx
@@ -612,7 +612,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>23400</v>
+        <v>28800</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>136800</v>
+        <v>131400</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1228,9 +1228,15 @@
       <c r="E12" s="1">
         <v>40</v>
       </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="1"/>
+      <c r="F12" s="3">
+        <v>45677</v>
+      </c>
+      <c r="G12" s="4">
+        <v>600</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
       <c r="I12" s="1">
         <v>70</v>
       </c>
@@ -1260,9 +1266,15 @@
       <c r="E13" s="1">
         <v>41</v>
       </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="1"/>
+      <c r="F13" s="3">
+        <v>45678</v>
+      </c>
+      <c r="G13" s="4">
+        <v>600</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
       <c r="I13" s="1">
         <v>71</v>
       </c>
@@ -1292,9 +1304,15 @@
       <c r="E14" s="1">
         <v>42</v>
       </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="1"/>
+      <c r="F14" s="3">
+        <v>45680</v>
+      </c>
+      <c r="G14" s="4">
+        <v>600</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
       <c r="I14" s="1">
         <v>72</v>
       </c>
@@ -1324,9 +1342,15 @@
       <c r="E15" s="1">
         <v>43</v>
       </c>
-      <c r="F15" s="1"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="1"/>
+      <c r="F15" s="3">
+        <v>45682</v>
+      </c>
+      <c r="G15" s="4">
+        <v>600</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
       <c r="I15" s="1">
         <v>73</v>
       </c>
@@ -1356,9 +1380,15 @@
       <c r="E16" s="1">
         <v>44</v>
       </c>
-      <c r="F16" s="1"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="1"/>
+      <c r="F16" s="3">
+        <v>45684</v>
+      </c>
+      <c r="G16" s="4">
+        <v>600</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
       <c r="I16" s="1">
         <v>74</v>
       </c>
@@ -1388,9 +1418,15 @@
       <c r="E17" s="1">
         <v>45</v>
       </c>
-      <c r="F17" s="1"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="1"/>
+      <c r="F17" s="3">
+        <v>45686</v>
+      </c>
+      <c r="G17" s="4">
+        <v>600</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
       <c r="I17" s="1">
         <v>75</v>
       </c>
@@ -1420,9 +1456,15 @@
       <c r="E18" s="1">
         <v>46</v>
       </c>
-      <c r="F18" s="1"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="1"/>
+      <c r="F18" s="3">
+        <v>45688</v>
+      </c>
+      <c r="G18" s="4">
+        <v>600</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
       <c r="I18" s="1">
         <v>76</v>
       </c>
@@ -1452,9 +1494,15 @@
       <c r="E19" s="1">
         <v>47</v>
       </c>
-      <c r="F19" s="1"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="1"/>
+      <c r="F19" s="3">
+        <v>45691</v>
+      </c>
+      <c r="G19" s="4">
+        <v>600</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1</v>
+      </c>
       <c r="I19" s="1">
         <v>77</v>
       </c>
@@ -1484,9 +1532,15 @@
       <c r="E20" s="1">
         <v>48</v>
       </c>
-      <c r="F20" s="1"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="1"/>
+      <c r="F20" s="3">
+        <v>45692</v>
+      </c>
+      <c r="G20" s="4">
+        <v>600</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1</v>
+      </c>
       <c r="I20" s="1">
         <v>78</v>
       </c>

--- a/LoanOfficer-A/2023/83 sunanda.xlsx
+++ b/LoanOfficer-A/2023/83 sunanda.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>28800</v>
+        <v>30600</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>131400</v>
+        <v>129600</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1570,9 +1570,15 @@
       <c r="E21" s="1">
         <v>49</v>
       </c>
-      <c r="F21" s="1"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="1"/>
+      <c r="F21" s="3">
+        <v>45697</v>
+      </c>
+      <c r="G21" s="4">
+        <v>600</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1</v>
+      </c>
       <c r="I21" s="1">
         <v>79</v>
       </c>
@@ -1602,9 +1608,15 @@
       <c r="E22" s="1">
         <v>50</v>
       </c>
-      <c r="F22" s="1"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="1"/>
+      <c r="F22" s="3">
+        <v>45699</v>
+      </c>
+      <c r="G22" s="4">
+        <v>600</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
       <c r="I22" s="1">
         <v>80</v>
       </c>
@@ -1634,9 +1646,15 @@
       <c r="E23" s="1">
         <v>51</v>
       </c>
-      <c r="F23" s="1"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="1"/>
+      <c r="F23" s="3">
+        <v>45701</v>
+      </c>
+      <c r="G23" s="4">
+        <v>600</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1</v>
+      </c>
       <c r="I23" s="1">
         <v>81</v>
       </c>

--- a/LoanOfficer-A/2023/83 sunanda.xlsx
+++ b/LoanOfficer-A/2023/83 sunanda.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>30600</v>
+        <v>32400</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>129600</v>
+        <v>127800</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1684,9 +1684,15 @@
       <c r="E24" s="1">
         <v>52</v>
       </c>
-      <c r="F24" s="1"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="1"/>
+      <c r="F24" s="3">
+        <v>45703</v>
+      </c>
+      <c r="G24" s="4">
+        <v>600</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
       <c r="I24" s="1">
         <v>82</v>
       </c>
@@ -1716,9 +1722,15 @@
       <c r="E25" s="1">
         <v>53</v>
       </c>
-      <c r="F25" s="1"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="1"/>
+      <c r="F25" s="3">
+        <v>45706</v>
+      </c>
+      <c r="G25" s="4">
+        <v>600</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1</v>
+      </c>
       <c r="I25" s="1">
         <v>83</v>
       </c>
@@ -1748,9 +1760,15 @@
       <c r="E26" s="1">
         <v>54</v>
       </c>
-      <c r="F26" s="1"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="1"/>
+      <c r="F26" s="3">
+        <v>45708</v>
+      </c>
+      <c r="G26" s="4">
+        <v>600</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1</v>
+      </c>
       <c r="I26" s="1">
         <v>84</v>
       </c>

--- a/LoanOfficer-A/2023/83 sunanda.xlsx
+++ b/LoanOfficer-A/2023/83 sunanda.xlsx
@@ -612,7 +612,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>32400</v>
+        <v>33600</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>127800</v>
+        <v>126600</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1798,9 +1798,15 @@
       <c r="E27" s="1">
         <v>55</v>
       </c>
-      <c r="F27" s="1"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="1"/>
+      <c r="F27" s="3">
+        <v>45712</v>
+      </c>
+      <c r="G27" s="4">
+        <v>600</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1</v>
+      </c>
       <c r="I27" s="1">
         <v>85</v>
       </c>
@@ -1830,9 +1836,15 @@
       <c r="E28" s="1">
         <v>56</v>
       </c>
-      <c r="F28" s="1"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="1"/>
+      <c r="F28" s="3">
+        <v>45717</v>
+      </c>
+      <c r="G28" s="4">
+        <v>600</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
       <c r="I28" s="1">
         <v>86</v>
       </c>

--- a/LoanOfficer-A/2023/83 sunanda.xlsx
+++ b/LoanOfficer-A/2023/83 sunanda.xlsx
@@ -612,7 +612,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>33600</v>
+        <v>35400</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>126600</v>
+        <v>124800</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1874,9 +1874,15 @@
       <c r="E29" s="1">
         <v>57</v>
       </c>
-      <c r="F29" s="1"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="1"/>
+      <c r="F29" s="3">
+        <v>45726</v>
+      </c>
+      <c r="G29" s="4">
+        <v>600</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1</v>
+      </c>
       <c r="I29" s="1">
         <v>87</v>
       </c>
@@ -1906,9 +1912,15 @@
       <c r="E30" s="1">
         <v>58</v>
       </c>
-      <c r="F30" s="1"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="1"/>
+      <c r="F30" s="3">
+        <v>45739</v>
+      </c>
+      <c r="G30" s="4">
+        <v>600</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1</v>
+      </c>
       <c r="I30" s="1">
         <v>88</v>
       </c>
@@ -1938,9 +1950,15 @@
       <c r="E31" s="1">
         <v>59</v>
       </c>
-      <c r="F31" s="1"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="1"/>
+      <c r="F31" s="3">
+        <v>45754</v>
+      </c>
+      <c r="G31" s="4">
+        <v>600</v>
+      </c>
+      <c r="H31" s="1">
+        <v>1</v>
+      </c>
       <c r="I31" s="1">
         <v>89</v>
       </c>

--- a/LoanOfficer-A/2023/83 sunanda.xlsx
+++ b/LoanOfficer-A/2023/83 sunanda.xlsx
@@ -612,7 +612,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>35400</v>
+        <v>36600</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>124800</v>
+        <v>123600</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -898,9 +898,15 @@
       <c r="I3" s="1">
         <v>61</v>
       </c>
-      <c r="J3" s="1"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="1"/>
+      <c r="J3" s="3">
+        <v>45781</v>
+      </c>
+      <c r="K3" s="4">
+        <v>600</v>
+      </c>
+      <c r="L3" s="1">
+        <v>1</v>
+      </c>
       <c r="M3" s="1">
         <v>91</v>
       </c>
@@ -1988,9 +1994,15 @@
       <c r="E32" s="1">
         <v>60</v>
       </c>
-      <c r="F32" s="1"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="1"/>
+      <c r="F32" s="3">
+        <v>45780</v>
+      </c>
+      <c r="G32" s="4">
+        <v>600</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
       <c r="I32" s="1">
         <v>90</v>
       </c>

--- a/LoanOfficer-A/2023/83 sunanda.xlsx
+++ b/LoanOfficer-A/2023/83 sunanda.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
-  <workbookPr filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3000" windowWidth="20640" windowHeight="11760" activeTab="1"/>
   </bookViews>
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'MD50000.15-DEC'!$A$3:$N$32</definedName>
   </definedNames>
-  <calcPr calcId="145621" iterateDelta="1E-4"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yyyy;@"/>
@@ -612,7 +612,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>36600</v>
+        <v>37200</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>123600</v>
+        <v>123000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -942,9 +942,15 @@
       <c r="I4" s="1">
         <v>62</v>
       </c>
-      <c r="J4" s="1"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="1"/>
+      <c r="J4" s="3">
+        <v>45806</v>
+      </c>
+      <c r="K4" s="4">
+        <v>600</v>
+      </c>
+      <c r="L4" s="1">
+        <v>1</v>
+      </c>
       <c r="M4" s="1">
         <v>92</v>
       </c>

--- a/LoanOfficer-A/2023/83 sunanda.xlsx
+++ b/LoanOfficer-A/2023/83 sunanda.xlsx
@@ -220,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -290,6 +290,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -400,7 +403,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -435,7 +438,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -819,7 +822,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +831,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>37200</v>
+        <v>37800</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +860,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +869,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>123000</v>
+        <v>122400</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -986,9 +989,15 @@
       <c r="I5" s="1">
         <v>63</v>
       </c>
-      <c r="J5" s="1"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="1"/>
+      <c r="J5" s="24">
+        <v>45861</v>
+      </c>
+      <c r="K5" s="4">
+        <v>600</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
       <c r="M5" s="1">
         <v>93</v>
       </c>
